--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FHD_Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{334154E0-CDDA-48D2-8D35-7F29ACF75630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93318457-E69E-4CE7-B44A-3D9F87030B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="127">
   <si>
     <t>Device</t>
   </si>
@@ -395,13 +395,19 @@
   </si>
   <si>
     <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAYEBQYFBAYGBQYHBwYIChAKCgkJChQODwwQFxQYGBcUFhYaHSUfGhsjHBYWICwgIyYnKSopGR8tMC0oMCUoKSj/2wBDAQcHBwoIChMKChMoGhYaKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCj/wgARCAGrAasDASIAAhEBAxEB/8QAGgAAAwEBAQEAAAAAAAAAAAAAAAECAwQFBv/EABYBAQEBAAAAAAAAAAAAAAAAAAABAv/aAAwDAQACEAMQAAAC+qAAAAAAAAAAAAAAAFwx3rwcj6Dm8RHrRwXL6HofO9NntmG4AUAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABnfjQZxEUtYXCdGQzUgcl7TJ6PZ8/Fn05xdoAUAAAAAAAAAAAAAAAAAAAAAAAAAAAGRz+aY5ukzYDojYgkqxBRi6DNa5B63mZ2fRV813HrnF2DAoAAAAAAAAAAAAAAAAAAAAAAJI8W+eNCXKU0KtcQzeVce/B6tkt6mL2kjk7vLj2uffEWd5S67ctnsdvzW1n0BnpQAAAAAAAAAAAAAAAAAAAB5/oePHLnopTSNxNlGNpIz0UvJt0uznNaOS92uE9WBpn08ZKahbYbkYdOBp6njdFe51fL+qnpgUAAAAAAAAAAAAAAAAHP5lKOe1UrqbHKizTO8105+hRospK0xtHU0sgEU8jOaZDzDTNWY6rQ1y0zOn3fjforPRAoAAAAAAAAAAAAAMN/LjkIqWdUx5bSiuJq+d6Sl8uR1rizT0Z4Gde3mpfVrzLPQnOyVoGDvMqlia4tFpo59Y1Po9vl/pbLAoAAAAAAAAAAAF43f50TeFReXRS408UpRyHXyxCuCiSsimMTQaS2LXn0Orq8rc6s7CU8REiu4SO5Zl6vk9B9QJ2AFAAAAAAAAAnzx52G2JWpUZJtZ565BYsHQEiolNAqYmg0VSkFNUwNduRHo4xoRHRgTUUSNDJo+g7fF9qwAoAAAAAAAAPJ9LxoLVRmqdSHNLjjeRpDCiKBATcszLozTSXStZlOmqUNgPo56NppELTMz0UlPOzb6f5L6izUCgAAAAAAARwcOsSl52Jpmfn9PNGaKFSQTUjoSOKFTYSUh0qImoKqWWkwqJNOrg7jKdsiZuRVFh7XjeintgaAAAAAAAc/R50ck2S0AEXhXJhvhDZRMWhMpMm7pJiyNxNZ2DUFzLFSDQVkTaH0YaGmemQwozkCurj2PqQLACgAAAAF4nr+LFVNy6Z2Vlj0cycahy6pUQiqARNTYKmQyIc6QOUxAUpqyqCFIFJUdWHXiYUmLHWRW0fWVhvYAUAAAAByeR6HJFVlpLcSk04e7gt5rSis2BUUEVFVpnsCREpMAYotmbRS2jQG4iGA7hnbneZkpsiaZnbg+m6/J9awAoAAAAR5GDqVaQ4ZLK4+zirkJcWkypUlE3TvDQqamMykAQOkAOTUHTUuHKskA7s6yMp1xNZujB3mel73zX0tgBQAAAcunjxOy2lzSzK1zC8Npry5vMolxOkg6hU6VDTyAHCTAGE3NhWVVRLFUEaPLpNsNpFn0QZDZlG0G31Hyv1NjAoAAA8/kqYp5pYdzFCRdYi8vL6PEkyUFZ1SSCrysrKoCdJjTOpp1UA5sVDEVMSqZPbz9Jmnkb7cuosN4IhsPrPk/q7KAoAAFHk5AZmmQJ1K9MmaTN0/O7iPHNchuQuXJWmOtRNyKkxhBbmoTSHagbmySek0y0RSGKWg25tiMd8ifrvk/qbNQKAAi8zxwyi1LWSdYqkjNuTWSjDh9XmOLOkDFVtBMaSJtA1QqTgluhAOqCOxTDCC2gU7ZGWs6lc2sGX0nzfv2eiBQAHB1+HGpEQTLW7zo2SZlltIWUUnCc/L6cW+UujKKJKypVDIulUyXDZQWTa1g6KkXPtAAhuNCYvEqigEzl9zxe+voQLAA87zqUaYa5xGuVFbY9NLObM5pqXnpBVSKKVRltUcmHo5nn11ZHOuhGD7JMTp0OLXoqk2oibzJFQ1OgqpmE78dbmbi2kJ5TX2JNWGG/mHmbY75sxWYlrRaTDO8qqmCvPSNJQPPSAipNMxGjyS6qaJapFKo0zspRShw+cRWhlo2VG8VPLvzRrUUXnUl5Mr6qpqw8f2PHji2lQsrpTPHqLrOhQ5KQh0MuVRbmiJuDHaZKy6YCaFaBIrPQTrMYQNygzuTSKsi40qM3CUtJlDSBRFn1GnP0WHkev5hyRWcPGqWi8wVKjNXBthsZakVHQ0IpI8XUuWqVXmKNc6mryojLdALSTl1uRK3Zg6SulYTDIGh65ak5UyE0fSdGeiHP0B4EejxmBoSvPbASoKzqBdeOthUZmyIXXN0YXKjbC8y5egZJFEhVuSpvMbks0ycGmGrWFrlFRoUgQ01CCgvH2K9BggBS4+0jxI9zlPLj0eVYl5wp3gqHSTVZrVxRE1maOsl1yYjxtE1SM6qShUNqSdXBpzaoVSwWexM76nIdnTZ5c+5seFr7jOHvAAKAAAAAAIQwkoM1qGEdQcS7g82PVDyMfdD55/QEfNH0iPAj6Fnz8fRpfn695p89p7xXz2vuh49+qHm7dgYa0AAAAAUAAAAB//aAAwDAQACAAMAAAAhAAAAAAAAAKXNGFKAAAAAAAAAAAAAAAAAAAAavyr7LmHCAAAAAAAAAAAAAAAAAAGbnVuCrGfmGAAAAAAAAAAAAAAAdTHy4E8QmD6GdIAAAAAAAAAAAACf587LF/Kiku3rorAAAAAAAAAAA1HGxITOjH+DtdRXj5AAAAAAAAAGKDvte6nnrqXlV2bjSoAAAAAAAA9PXzDWDnrveijm2Sz7iCAAAAAAWhDfbDDvnP2X7KerH7R/qAAAAAAA/lnHLr2HH7eZzP7XpBjhAAAAAEY9lTTH2DXzTbDr7uv1TH/AAAAACyL0n/3b9jTH3TjDnHvT3+CAAAAlBA9bTVzTZn7TNR3/AH051YogAAAMYy6Kzx66R7w57dZ9412fW6gAABGA7/v62+7W33zy1zy/zxzvwQAAA8887LU929x4w2yyo47492/xQAACx8+/iwzVR9w1Z1iZ8/2yx19QAAgcw60Tu40+86557p6++95w8wQAEFUF5jl9miR8+6zzcRe452yxzQAHg321t/16NgYz/wBlkps+M1+8tAABl+/lW6/fGt4dvct1q38tPW9/ggBpeupbLK9++v4Sc8lOdOdSqsuEhKPcaL/fttIbudJpde88dM49fNqoIcs7B8d3+98FtwYeb+nQ0+v1GQJJ3ess+3v5JcIMMMeM0lwqWl4+CICI3BTtusO+C69cN9+tcOFM1U8IAAAAKKIIJKBFNOsY91FOIIIIAAAD/9oADAMBAAIAAwAAABDzzzzzzzzzJisI8vzzzzzzzzzzzzzzzzzzzylcd6Lodz7zzzzzzzzzzzzzzzzzxZZisLZIPhHvzzzzzzzzzzzzzzy+BRqi6r0+ysYrTzzzzzzzzzzzzlz4qGpskBSXVxrizTzzzzzzzzzxJ7/enIrd49NP9t5aLzzzzzzzzyk7aMusnfu5U18uXqINPzzzzzzzzY/rM9u6Y77Mca/vL5br7zzzzzyttvpqIqrqLYe699rkhcJXzzzzzzscup5bqrYbtKZIKMGaJq7zzzzzjYDb6p6KPKqKa5I4tY5QqfzzzzylM7L6qo8vzbJ56pJ6JIJJL7zzzzstpn4rhxx6Z7or5YobLCqFzzzzw0JPgI6qRrpp6JpoaZrA5tRXzzzwzpLE575zrIJYaaApLKJIfpbzzyApIrnBpbQiQY7LKSS6rpIpBPzzjfzpKLoqh5BS75ixYY6ZJ4ZJrzzr5n7a64b4YDxRrIP65L55Y4JLzyzr/wCr3+y73FYg0SPDniGEqGeq88FDuWS6GjTH0+80KCneMgeSiy284HH71DQe2kyGGK2qS3aueWkGGXUpeSK78wmeGsJy+jnbyeaWJmeaa8vHyu7Ci+COm/6ML2qyiaq4RGTf+tjKWg2OQUBCySBLyvunUwcsauO8UdQqkUL7mI27KSuii9adnMmqe028mJxH0fkAMiRUAu62i+gGEZBMm8888++Owdsvqz3rG74qskOe+8888//EAB4RAQACAwEBAQEBAAAAAAAAAAEAEQIQIBIwMUAh/9oACAECAQE/APitT1PU9TFl/wAq136/kydJeq4J6g3/AALpNEMSo4hEGOIbumY5fbLX6wNmU9S2WxZbDQ1PX0XRCLDj9hH/ADnHJfllpIQj0beMcviv8Y9sfuMXeP52ul0vzYnGPbBuJ9l0Gh/3rJl1CDFrgNj8iHOWsY0Q0GxiytrytaIcrtPmm6n5shyt/BPsPCwNXLuB0vS1ysx+Y8htfhjtlXrKB/JjwtQbi1L/AIF4x3lp/wAgX2vbloeTa1sn5wwO15esm+xi8XT8Hp5JcuVA3+yvjWkhBmXDBlQOg4JUSDK5GMZ+6WEHdxa7GXBvQ8ENuMqVKdXDKOXFy4vC1LhKWGM8wOalSpUMSeCeCeCVPM81KniVDGeRngnkldf/xAAfEQEAAgMBAQEBAQEAAAAAAAABABECECAwEkAhMWH/2gAIAQMBAT8A8vmfAz4jj+YOkJX5MThyqXtJUr8GJsbjFYLPpn07yJ8+xtygacYY1HGGJKhF0hHH0CBHhdh3lieRCXFvQfy+Q4/1iVtPE5/5zcNLUHh8DyWoaXRFrhK7Ox4CDytby7xx6G/FeXoLhpPxPWGl/EEesdj+BNMeQ/IusynjEv3DwzbeMWthEcv88hvxy4INOyVT4pXjlwT50tQ0sxfMOctkNjfAxemEG9jfGRsOR2EZ/vLMfDIvRD+bYEIt8AQxWVpOx0kdG76WBCXUW4svoOFrWOwi3tel2Olh06OKqLcXQSrZVROk0MXY3pa2MMpZDK4pP5ze65CNRajlPqo5S78bn0z7Z9s+o53HKfU+o5sc7n2z6WX3/8QAQhAAAQMDAgQEAwYDBwMEAwEAAQACEQMSITFBIjJRYQQTQnEFgaEjM1JikbEUMMEQIEBQctHxQ+HwFSQ0U5KiwtL/2gAIAQEAAT8C/wAMarBq4I/EaGbTdCd8QeXcDWgdSm/EKpd6E34g4uiwEJjg9ocND/lpMarxHjc20t914h9drpvdG5leaXuDvMJ7SnF2k/NbySPdBx8toaE0ZIIt6u6ojHvrleH8UaDgI4ehVHxFOsOB3y/yutUFJlzl4qs+o3t0TMgQQH7I1Sx/Fcbde6cASSIC2kmeqFS7QcKDgN8fujOnpO3VbEHZEziJ90wvbJqanSNlR+IVQ5ujmofE6QdbUDmlU6rKnI4H/KPH1vPfF0N2HVOMDiyDsmsteKj9NpTnODxjhj9E0AweWoQodfxDh2XllzoxhPtputQptvh1TiiQvIMi0g9UeEMht+dVWcBVsM53UCOEY5RhFvFJ6qqH0iKt0Hq1fDfGDxNOHYqjUf5N8Rr2AU2nico1BggHJW/5hkOUl4Fx+Spl44Hwe6NMeaXTa6FL5AMOpkapgM7BicQbmwO5KNrKjDZzbqXa+noF5cEW4G/dPcWybZjGUz7o+YTOyr1A2k0n9F5ocMudnhGE0mhXBogC0Kh4+k9ouNpTXBw4TP8AkfiKopMk67KvLyXPzJ/RVg88paCh6RPLugA04bk6wiAKczHVBocB0UsFIzr06IOJbxPE7J1OW8cdkHNDWa26DuuLcXZRxrNxUkbyAYI6pzm+aOHgcNUBzHhs2VOlNa7iG5B2QYG1HtZkkTB0Vo+9I20TXWP+z8ymdoKofEHsafP4o6Kl8RoPMF1p7/5B4iqKLLnfp1VWs+pUl5z22T9WjqiI+8EfNVMsPUag7Jk+yg2y5gx0TTOgmeqaIDmvPHK8YXUfD1XswWaKn8Truk8Et6leHd4mrVDKb6V0n1Sms8WBc1/h63FabT1VU+I4x5/hrqfM0OVH+JixlXwrnRNs5Tf4uKXH4amag4QSnDxopjzHeGpNmAHFeK8Z4nwlZ1GsKZOuFR+1osqQW7x0TJEg57KkXYkfJVDNnlki3bqg0hhNo49AVT8TVpOind7OXh/iDHmyrwP7/wCNe4MaXHReIrGtLyNNAtAIGqYRc6TheiR/yrZzgndHSN1aQ0ZFqoERdHWE2CCB6t18UBb4KobpxC8DQq1hUNISPcLw1GvRr3+WXCXGJbuFQoOoeFNNlJ9znh7uNv0VURTrl1Nz5GA4t4VZSHxB/iKbXPqBlpgiE/8AibPD+X4Si99IRdUcPoqn8TU8Mxr/AA1GpVDrnXOED2Xx653jPMc20ObgSvCu/wDaUs+lPP2tzRMdN0HkhzX82yacxM9caJj7ja192MXLiinluu+68YMB268B499Hhqm5n7KjVZVZdTdI/wAX8TdI8sFMB4v/ACVBa3h31Ct2n5prdgMeyaMTJ/RWkaRaUzNTidIGjeieXl/FAA0V7mXBxDepC8U8RbW5X4A7JnhaLaga6g58/h2TvAUQ7hpcO4uTfBeHGCwYX8F4Zwu8q0f6lV8H4cvtstR8H4UERSx7o+Ao3fciN8o+D8MH2+SHduiAabdTbgdlVLQ8tcRcqLpYA6WymTLg3Y4UNPmNpnimYctc4kaDqmuZUcQWls7o8/ZeDr1aFZ3lERu3qmfGKZ1puXh/G0a+GO4uh/xPjnH+Iedkw4kz81BGRgKH4jmTRc3Om6YduIT30TzFE3MnP6qq+oylSDScniKqujqCdFDG1Z9UI68XEN1Vc8W2wc56Jxtuc4rVxwc5WbBi2eqd5rOHmOrSiX4EC31KpWsa42nREseKYyT1Wg+0/UKrR8vxBfzteNE+YUAY9PTqnBjy2oNCqm7tmponO4yiA20NGp6qW3kElpTQw7gkJ1MuNwdavA+O0Z4hwnZ3+H8ZX8mnjm2RcDjVyqSXNBweiuNwuaT1WIAcMbFN1tdBCYJcXHDh9E+oXO4TGyqO4gyLnwjktBw7WFoAAPmnOD/EtbJEf/shbkfqnxPNaDv0QcPKALuO79U7hDoudnIUiIouPNm5Pozhpl23ZPE80GBDymttHLMDDhqVU4XUyOXT3VTIFNxDu/ZVKfDa3SYCtthpzhS0R06J2TP0T6jDIicZHRObDmuI9ky43zbU29k2m1tz9O4Tw62abgP6rxQc1gOnZfDviDqcU6xuZ16IZ/wvin+ZXJOxgJ2BKJl2Nd012SOyEWYk/wBVRLeWT2Ce5vmBs51KaDVq5PCByJoIraghq+7qtAZIqTjdOdItpkNcduqoy1v2nE4bpxFsVC2Ad1WIDy192fXsqQ8z0SwY7rxFMcEPLXzgrS9tRwuOU3imOfcdEWnVkdxCbwy5xLrsT0Q4gcC0HGV4h19MloPRUqNlWagJxIkp4uaWkcUzqoe1xu1QcS0QD79SgBLnOi7smAQMXNOqa2J6ziVT6E8H7qQRuOq8UWkAagnCbkREL4N4v+IoWO+8Zr/hPGPsonqcJpgl5GBqnPupktkO7pzWNcH1H5tgFTEimJHdUgQw2wYO+yc+wwwcL8F3+ybwwHCG/hTCKb3lxHFoAnNuqHLbxgqtSP8AGU33Q1MpWMhktbOiDSKc1Dxp9nlCTbcqxoFtpqH2CNcWANe7G6HiaQIw5+ZhPrM8wua33kaqnUo3z5h0VIufNhETzfiVt1fzHZAEBcApPNNrVT+7EOLp0lU6IBk4adJ1QLRb5jeKd1wm+oduqZTtdjOOJNpN1IGdFVq+Q4BrRnEdFVdc0uHsUyHmA72lPBYPxyqjvsWNeQ4zhOy7SCqDzQc19IG4GT3Xhq7fEUg9n+D+JPuqhgGAvE8jaXXMprXDcyBqoNp4JV1Ns3DlEymxUgt5XD9U2ly+Y7I2TvEXOtZF3Ryql5c1rW3bFypNqc9Ucpj/ALq9j23XxE4dun+IIc2MQIlPrOqWiJnJleY4nqChWbmR7prg0aDIQdB2mE6prGPmi/h3/wBk7UBh0TXva4PDj7aptYPEOjOsLQS37QgadEbg2HZkTBQmy+23HzRYeK4jXI2XF5moLeisLGObePyx6U5ruZ+XcpKc5rOd5jZXCM9MQmxUp6THVPDY4yP9lH2gu02VU4ndeHrP8LUDm6bt6qlUFSmHt0P+BOE83V3E5kqXOLjxA91c/IZm3JTXu0OhzKqvYKVmknToqTLKgceRowUKhtktDeisAZdF7uoTWtgXcAaOXdeK8TlgaJ7oVYkvydMq426j5pxJ4cx2WmRoNliyY2Tc1PcapoEEkk/1QaBzZTcDkjMIdfohjjDtdVdppaFfB4HlU69k+Z/wm8UHFo3Tiad13E3VXX1LRAG3dNu8vGqcAxreHuVIL3Fv1VQyYae5TXXh3nH5BRFLi4uiaeLi1O6rnf5JoLnkYyvgniON9B3uP8D4+tay0alXGlTxBcUwPc251VxztumttMek69lTBbMQAVUNMZcycRKfHCA/7Ocdl5n21xAZsCd1XIp8vE45DWnVGqS6S4OjUq8P2UB3Uwsq7H/mUQMu6ITOcT9UMsgjC9REe5UdwsjhnCAbkRqqmOlqFrtP1QluDk6e6D3XuaQHN7oSxrjTIx9E2s2s3mh6knj8vOiPFrFus9E8RUvyamwauElgM4OpVMAseXerVOI4ciS3VSPLudNp5hopIJESnvuoxsmkjhA03XhqnkV6T3GY6IGRP88rxFXzKpI0VRg/iZdMJg8wgD0qGaTcnkGpYDy5IXiDwjIDLleGXvqtw3GFUqA4tF/7BVIBs9P1P9jGwNeCMd1/q12CdxQdCnEAniyUOQk5hajIhdRONk4uGPqnAHOrlcGgkN4V7AxGU4ZuJA6qPl3WXcjdk2Y0IKmKgaJPum8fNDXHACpVJc0X6dFVp30fsyfMbo5Nua43PblOpu4p3KcePGU1wyCRCY0Fo9Tdcprw97u2hVX2TBGd04XMJbGv6L4VU8zwbcyW8P8AP8ZUsomNSmD7SdihBfuNz3UtYwN5Z6LXAZbOvunxkga4TmywBs64Ves4YbaTornNDrYmdVaHqI9v2RzEI7AO01U6Y02WCYwmwSTpsi7U9SgAeIImehBRecelY6hMmAZx+6firocqSJaI7FAfKN1JInIlHBwNUDFo9I3TTD567DdeHIy245xa5OHls04nfsnAcL5OM5Rbe4G8D8XdOZwgehxlsLQ8W+yaAxkNxKOI6LQEyqb4jiEalfBHxXqM2dxfz/iNQur2RwhMB5gMaKWmAW8WvsrnXvfEnZVyajW2v8sHUoQ7hcJjXuqxsoHUbInU/qU4w7iOuZUg++yiXi2TOqmToMJzgI+iOdsynAMGnzUyRrI0Czr/AOBGC7OwQ5dPkvXwj5lNy6Y1xBQmYdrsplqg6Qptb7aAqQXSHaoO4pxGif6YBkbLSOESm4k6dVRfcSXENI0xlMIFXiqcZzapEOvfcTn2U2M24h+iiM6hObIbEnqOidka6IaZUND+EjOy8EfK8exw13/nV3+XTJTjnWSgwlPBc8YhNp8ctIIG3RNfcwnYo8DWmmIa70xoqtW+oDPABhOJ/wBkzpo7ZHLCpcGTAnog8zDYKIyBJTtQeqcWkD6IaaRG6kMFuoQMkdPSrpjEFAyzTdBpzrlcJk5na1E9II6okgEM1GyIb89yvTnCAl5mOytk+qFbyydNk24Hp2WWVQ8DOqeGufTdiNQn/eE4bTG/VOEsua24lHibPqCt4uaMbqNYP+lT/wBwmCeLA7KoXY0gjVeHf5lBjwZkfzfiVQ8LG9ZKjt7qlzEOg7hSS6GTd0Ti7VsdzCJiGdd14p1jB+KE4xy8xGZR5dwoEycqI1yJx2UgZblCI3yt4+iLrs9NUGTB+qcCeaO6M5t/RQ7HdHU9So+mU4QJjEQEGua2aYUzUB6J8+hvZNEuh3sUMHWB1TZ2EoZbv0RE/lACBPXQLBGeI7BMcRDL7cgg9E5gtIdxN3lNipBa6bVIwJzt3Tmm6XbItZaUXddlTIB/FOVUEv5tl8EqTRdTzwH+YV4h7i9z44ZRMEbziVHHhoPWeieLXOqSY3hUmvGBFqtkkSe56Ksb6kzwg4Tsulw4ijJBa1p7oZdp8yrOIfqn6i7m9k+bmDSd1uSMQjIG3dOJBAGhVlxEg41CmQDmUYmBIXCNvdyeZn6pgjH0TY8sGO6BmHJwg68PRWkm4ddITm8I779FvjZTLA/osnDxqsH32WOi4mua7908C0OlsfsU+Q0fRRGY5uqIAk5zr3RMLr0hU4iIE7qzJdI+a+CPtrVGn1fzPHVfK8OTumHvM7KZdByR+6icHUmCnZabmgsiCEBZFqrfZMqW6HfdE/YTJhH7u3fYLYD6qOKDMdU0YcN9gqbRxEfonDhluUXACeJOOB6huojA+QKnXtunXXaTOqw3NpgJmRndTEgi3ZRpbspExrKknZN957oyOvumj7TrKyMbphJY0dl2AwRKtmBJ6+6qYOPmolpDd9Z2XhTNMtMSDrGqcYAa7mlOIbLybsxlYcOWJ1RDWtMhWiwRqtBKbjTXuvAOLfiFPvj+Z8RdLg08oTYt4hpuqgiCOb91RHMBMlSDEMPSOqjbGPovFOhrQ3M5yqzrQ0EItGXfLG6jfrsot5TG8pwyHKLWg/utNEeh/wCUzcfTYLRqJnLciU92hEe5RnY8WqbrnROBJZcnQW4TZtbBmML0anWVsMfJTtqrjfgLBMJv2jQAYzhE5nomzPD7p0HmlNIE275KoGK0ekhVfvAQzgGhVrHYcMO6oi3LtTiRsnAxDXe8oy0cSGBxcunusGr0Kon/AN3T/wBX8yq4VatR3MyEG28pyeqGxGZGi/6fc4RLosqM09QVBkC66ScErxdv8SGnFo2VQ/aOgpn12R5Hfl3ThMdCtDiJT3WT1OyEjf2UGFgAThYKg+3ZRBBMKBBnTVPx0PZYMRGn6KQGS4wjw4UiMaouOYBTzwmPdZmSrXQAPaVHCIGFqIn5KU88Mt0TRwc/dNi4INhn2hLsTAVS0uLX8zTmdk9vU4/CnCcu+SqOjW736IAHrjiym5e7EKTfPQphlgP8rxT7KD3dAqZ68v7o9Hcu6dBeLIhPb5jC0ws8zRx/mVNsVHlvq3VQ3eIqEjsn2l0uytSptaBTGOic466dVZbrodUYs9kNhCcQG6/NBv4iCeiaMZHyX5fqpjm/RNAuu9SaDcQN+qmLuvRWl0wBOxTAQSJUmdRGqz1n2TgS7H/KOTke/ZEDMISBvhWgnim5CAOoVoPW3T2W5EahY6aLMXwOxVa7iBi12yc3iy1OI9Z4UZu04O60L2jTqpOmJXpj1LwRnwtKfw/yviJ+wt6ry8i46bjdU9CHOn3TW/aTTiwjVMN17dx0TKgde1+rcZTWRYBNkzqjPm1867rXmQnaLuidOC1vunH/APHop3d+i17dUzibLZRGu5Kj7XI9nICY/RNPFbrvCqjTvsUMMnMDRMP5U106THdXQSE4W5cDlPlrxpCyeWMYKzOmAqUy6dU0SMtTjGdwoDv91HHnbZVMtgfNFwENgk6J2NiqP3LZmN14m1ov7foiR5QdOE7XbATqYc1sO7oXvud9ArctOcaq0WmNCV8Mdd4RnbH8r4k66o1mw1QFrYnHROZdYMujWE0cxdE7W7qpLLWs4Wnoj9g4YkOXh2ANx1zlHneZHZRMyszMwNljcuIVWOWOJMbqRM7Ik8wnuFEO1QnQfi6IAXTn/SgZyUamOUknsqkggiS1qgGSHEJoLQM+4WmLjroU1pvmQR1V3TB90YxMLMnv9FnssHiBPVSS44+aMW8WN1J2HeE48U2nqidQ4xsmuJHF+iu21THm1tsd8Krlzca8yIDyGnG4Ku4wzF7t08OYMbaqYYLOTotLtbdjK+7YbsxlfAKt9F4OP5XieLxFSDhVJDPs4KBBgtcWmJ90xttPL9c5Vws99DCqTY+0XO90HFtoGcZ7qpw1nD9kZD3ZDuyY64ko8RFpCjX91J6DGyJxnTXVDnBOkxlCpqMkzog7Gq3j+i4Y4TrsrSDA5fdFgxsnMHMYP9U0GdY3RcS4y2I0QJ2juV85Cm3HpQ5fbKaW/wDZBucJ0XW/Mrha+Nz1RydYauhtydkCYgfVGA13/hUcLQ4xLRaq/wCVcInsnOhhfyucIClvlsEx1CeM5PCNFSaeEyC3Qq62QGn/AFL4EY8S4dWz/JOifNz3zumcIALh1Ximl1EBvMUacFvFkc3dNEN4bmj0tQMvM6E57ryrrjN3QrxI4wYIkZCc3iJzjSN0YtH/APKaN0BnPyRJGd10Dd0JxdCgNM/iPVGGiOVCJkcygSMYGVVwRE4OVgzPFHVAt5tlMT+HWFVw49dlkSHZWuAjrIAO590063HTomtjM+6a6Xmdk45Jz7JxAE4vKO+f+yp6Y9iseZyoiX99lUNznCzSN0CAPJmLU4ScZQ5bRiwyouOR7dlJqME+nfum7CI6K6MQddF8JeWeLYDJJ/k/EKoZQInidgImMu9oVMB78CE6pDzGY3TnNh2nZDzPNiQGx9VzQHBUwWU2hx9l4mSA4jTHuqsDIWOUc0xKz8xui5oLT+vZXC3Dbs/quhb/AMJrQY091AO6+gAUWjMd1vDQnOB7/NZd8tV/pNsp0Ow7rqo1H6lcWh2TMjHzKdFNojVyIHsojhbnqVjA2Xz+aI6CUCA2EDd2J2UhzsH3TRPiKf4eie0dQLimM+0LXEOgyQeihgYXGY6KyCNYO4WfLkninRNqAX2NtcN08h+JlEAPjpuvAm3xdIk7/wAjxNYUac7nRVqhf9pWwrCGgyBOhT8MxGPqpuaZHdQAxvbWU2boHDGpO6JFOJfxThOfa/L47dU8gseP0XiON5c2Rlc3yTfpugOKI91qD00XJ7dk262GiR0Rm4wJ/F2UuNrflIUWjinqnA2CDronxdw8PVC7oMaK1uo5juozmVNzscRUNWrOBo0UtHp91s46rk+8+cJtweOHGwU3EkLQzcdEOXhj5oPbnI7owWg9SvDCHPqGBGP1VRxGMK7AaHY2TW2t4QPZP4ahmfLjVXNa4CfdMiJZKIDTO+itiI4uyogedTjqh/f+IniCtPWT+G1OsNMF8kdU0sZTlo1QBaHNLwZCpU5iYI1M7px4jfoNE4Nsg4x+ijzDPmxacqmWxHNvK8Sy2prgp3OdYGqabm/0KMkcLdspzZKy4HHyQiLZQd9pPKYTXh8HU9EWwBc8+6frG2kL/VGN0yMszG6HDUNzDCg6hWjzMDJ3R5cfqhBa4EfJO2+qc6D1XFMvz3RwLRPunfRHO4hAj04P7prZkk4jCd/RU2hlFrTq/jKdxEzncK5rsNGnpU8DSDqYRcJDPrKcKV9u59SLS2Wm5vtuvMD4Z01WkHQOnReGFtVgP4h/IrONV1QvEZtXmOvcymBIwrnXcN3B2wqj50IDm6riJBdDh0hcjQbh2TDoX/VUw8GpaDb1Kuihc9vBMR0RIFXyacB50JXjQXw7/wCvUp8WjJyVlm/eUTcyY/TdTa1sk50QBudGyuHFdIWbYHTEpzy3HKP6IRkAn2VQaFueqJIAkQNUROXY7dE7Bb+wROw2+qjjxMcqaAHYV0CYMaFU3TrDe3VSVPD9EchwmBup+xjunwymYRxA7oa81ypUzV8QG6NBuKqZeXuz1QN2LSERUL5De68qmagIn/ZPsbADddU7Xa1ODiLNbsjsgHB0DJQgh+vEf0KZwVWmBg6pvKP77/vXe6YSXlzm2ypd/EsMHy95XmS2AA7OXaqnPmkMJsiZOyv44Dd4JTG/aXTtp2RHGIJiMBFxNmlp1VoL7huMBGnLcFonUKvT8qoRONkJY4nWOq0PCIGxQzAJ6/NDqXBqdl4mUS6ePZUhkdtltJ0Xf5whl9yquNzoB1Qyw6huy4oHb6LchuYKzo1QY+kJxuMRj8SbJyeXbumiWGBtEJuW/iA9Sa/GR/3T5fg4KDdAdinQ0T3lUaJZS4tamT2C8Q77InInXsuGy4GSuEOAE6JrJeD0yE+oGu4Rc8+lOLTU4eJUx0Is0C8SA18jhaRKYxwbHNJk5TdQc+6p8jfb+87lK1M91V+60mCo4YbLmDXuqgDGtNIRG6a9zqfALeqbcGuIYAT/AOSqgDiHOmSIEJtQBzHWYb0TpD3tuAceVWTxvz2lVXtZUDjqcKvRFWiW77FPERAxO61fPN7LRvDMotONHDeU8mcEYRNr5zp+ia+XcOE0QILg4nJVQ+n9FiIWmmf6oyZIHZaa8o1UZuu4DusDc2psIHY/JNaBUuMkfsrj/wD6RdENzhR1mUI3TQALgTaqDLqt1TlCuc8K4g7WgaKzQgw3ogJNp16pxMjInOOqtDGkXfanHsm4OlxUkMntGEQQ1rcE7lEw6JidCjn9F4V13h6buo/vVfu3eymA6YjYIYa0dd+iFQXW6YweqeWhrw+5yeXgA02cP7p0MYyeKXL7x2W479E6nxttPKOWU+hLnVSYdHDam/aNYHtMjqmWvElk9inO8vIDnSY9l4qnc6+k2fxBPbxAbHEhOxP9FMvwVkOOB3KmZLtlEcO5QHFw8MLXRNZYCX6aeylrGrpCsIxmequnBQME3K2Q0jhjZZIOQACn+lVBa2Yu7LlOddLky5rYkXOVvaVRp+a8tZsM9kXNENDSGjDT1T2B7hMXjZC3AweqcTY7h1yuOHEETujIpgxwnIVQa99HJrX2l0a4PdMYQ50O7jsrWyD+IQqtvL01TZc2NC5fCZ/gKc6/3q/3L/ZGXMONTnuE+mahLjIB0b0Ui4WEcPpKbTa9su1PdOJa3mLs8yINxGrA1NBE7ujVcwyLSTlQ5rnloExnt7Jtx53qBh2J9KbdcS6QTt0Rw6+8tzleKoTFSmJ3Lf6pzJJqZDuuytL3d1UAGPUUBtlMb8hsoEzlxGkpxkv7/REbmE4XaL5/JAZdk9uywILhIXqtPy7J3Ruw0WudPdOi2NdsqLRLvmV7z2VNmRGCRuE1pq/Z0v1QFl1Gk6Xer8ydU4GS06xHROcPVsU15e4uAAboD1TKl5LW9cqwUeQGBlA3MGcjMKo4DVp6wg8MtkmD03R5H5i3ZSGsba8u/oqnHxY4sSiAylaB7NXwMn+Dg7H+94+txCiNSgYuLj8leKrRHyUfa8TAdgU6Hio2d+ROLKTcnMSVRxS/O7KD7aQHq6K6ATgRuqrST5hOAdG+pVCBUdVEhowWlES7ijH7KLATPAPmSmZ+8Hsms+08wHHRVabS4+UC14OWdVBM2g/+dU45GI/onsNuoQHoO/ReonROPFOLRqnDTEr0Ear06rLeIwY0R4ff3Tue0bapwh3fZNxDoTQcFwFm8ppjXTZUxHPFybfVkM4Wbk6IMY2k5tHQ6ncpwaxgaJkhFx80BwuaBk9FY4NtPF+EpoP/AFGQArhUZDTHSOiPLdNsJp8xge3291VFoNx107Jjg8OPo/Yqk3ih44tlTLBVqU85zoq9rvDETEKTGP1XwN/3jPn/AHaz/LpOcdle51YO2dqnfezo1n1TSLWjMZITXON3DoMFU6jM3Dm0MJ4LsNi07q3gNgh7cLk4Q0HcowGi5sNTHZfsPSEGEvkxZCa3BYWgj2QEZBgp87nO/dEYlptC5n4GRlVKbfEA5hw9QVWk+kW+Y3Uc2yLZMN91LwZgDOE8xJGFm6cT1Kc6XENlxAx3TxwZ5tkZGu6cLpbiUG3cWcbI0/zHpPRHD+YTsmc92qLJgaoFrRAy4/VUvCkianC0Hl3KLWmlD2t8sajor3WxDWtOwX5eiE6xrt0VYgMBc63omEvm2cYHdVLrg2mLIGSmvbZa0nh+qY9tgIFk7Ko2WxJEKjiiM27+6aWz+Uj6p4IhvXU9E4OvL8WREdVVp2QBqV8Dfb4uw+pv934rVgNZ8ygZycA6QpaGnHKMhXcM4sO6pZcW8rdIThiH8vbZeX5dQlkWRmd1QG5BhG7JIh2/dPpk0g1oJT+dzW8/VMIcDjsQmFtv4Y3VsyNohQ3gPFjQJwx0tRJ8vs4ZRPKwkF/N2Cvc4yAXMOFUoAEubwcWGndQ5nM2B+qdZxCD7q248wMahM39MCVxTOuNU6bQnECdnbmFrxM4nHZWuhs6KB6zqVo6xoJk9E3wr3mahgdtSqQFP7plv5nLxBcGh44iNkwuL3C0gHqdEx9rncHLhF48385GqrETc7G0LV7h0OnVE1BbDtD+iunifjsm/lm/XsgAHM8znP1T3DzA0mHDOVYx9MXcqiQIxGiGYudiFfhodoT0VQg532HZeFf5fi6Tuh/u+KfPiX1NdgvDjg4kyo1z4bGkIxyuIhoglZNdovGNRCoNuY5xmS6UKk3YIHVyZpf5muXfmV/GSGOPRTJt9UZ7KG3Nqt2x7oBskgWlNZdFzsbLFxLfmiNziVxuMAx1xqnVW32GSevRcJdUZvpKl7LIPbTVPy+HEHspa3BwSdVUptdz0vZM8JLech3dP8M4s4HNN31X8P4gbAtHR2q8quXQaGOsp9CoWQWT3JXlVGxJY35r+Gl4vO2YTaFKBcCfdMcQJt8sFya4yRMQdeqJlpukdgmSx0XSzbqmmOabu/7pvDVcWwJXK57QSWhN6084ghNZc5xbrqeyh4aGNIM6ynXBksiejlUrAQ3JccL+uh6KuGvfamXuaTdrp1Uw4XDXIjqmW8T3C2FBn7Q4PLCe7N04VKZGO6Zyj2/t8ZU8ug476KouW0/XopDL9bOaSNEyTHnW/wC6q1HF0hstGqAfi4QdUbg838TfZUp80ybWN2TRzBxtZt1VQ/aXtPCNYTS/7xuWaR+FNAe0filNBHCfZNkDmbqg4+U6Bno5Am3edTOypxH2emsu2VYQLs3Jz7Q2cmP1VUggCSyTr1KImnrklVbneXBII3CJ1LtTt0UxvnYBOFs4JjPsiCafDmRKGoEe6utcA4Dh3hXOdUidpCdN/wBmRcM+6qEeRo5NIDTDY4VAbS/LKZBqEtnOCnuBfZv0VSy4sxpkdVVte/Di3oEfsgfLGoWXEgfMq12LYDt3Iguy3WE4PiJbeNHJ2W/ur/thcdkSC0NeDdrhEloGLnKb+HQo5rS3VutycBH2e40Q9I6lU+Rvt/b8XqcjBrqm8VbGVUHD88KqQ3IJd/unWglwdpqnXekASmhji1xdc6OibVF4Ek6xCqCPKKrZZYJx2TS180jPYoS3IHYxunH0uODgDuqbPKul1wOyZBbbs3RPrhjMDQJxD6WQRejxN9sK4VMNeC4agJ7ZJLRy6BNDgb3b6A+lZ8vPOUwYLcw7Uqo4Um21GzTRqANc7OdOypnPPMDONURpjOo7Kib3PdFsJtoY7UT1VwaB5mHFMt9DBd1TepOojiTGRQgmQhJFzm5jKcTc1scW/sqmfEO5Z2heVNSRid0CXVOEY0MpxhwNR2NBG6e4TNvJ9FLSGtpiQdU5wabWpzW3E6BeKEtKB4G3R3THl3p4XandOm3odkwxOOKJOUbSb3e5Klrp1uG5W4PdN0H9vxLi8V7BUIa57+qORwjMYlR9kW24EZ6p4LqtnK5upjCb96TSPAU3DKjaRMk6IgsDWtzbvuAn28NSC63lV4th2g1KYTkuAxpCiA4NmDsnZ2ccQELm0uFvH/Vfw95Y4u0zAKYJl3pacBUKbmy6oDN2Am+preTQQuHmsg+pYA6gnCue+TERp+ZNucGhstjKe8taSCHRt0VJ73Muc0Ov5V5YNS98i0qoDmyLNc7qpWa0w/WJlF0iJ5tMK/YtMaKDqdCVe2CWiNk4em0ZEhQLd+IZaVTMYy8bLLjpruVwhxgCfUVMdTOU5scbd9k0XPucce+ipnzS6Rb1TeF5zpo1OY8xaS1o17JzIZLsxylVuLExKFIZe7/hAOa1/lt3wosZLgcJ5DmHy/mFU0kAlpwIRk04TdOw0VHNFh7f2+MzXqJ44P6rW0ad15uAIMaEnZcoJuuYhZVNlIlh19l4QmCC0a5d+JVq8VYtJdHKg4sAbbOMAKreIjpnqs0qd1R4cJxCJY6m08WNE0zsWu6hFtsluZ1ygftg5ruxavEQMbHmDU15qXN0OkqmCGZc0s0kJhucQJkaynzlohpGjUG81u/0TYcB+w0KZJ8QXza2eXqpgNuxt7LV1hbhE9GYGic4uqFtocehVMRxtBuccyoh5eBr9E6m14Z5nC4bSqWcHi6onW75QuBjje0uB1KxwzIZrcq3EPL9TtXdAuEsNMSWjU9FT4W5kzop4cHh1TnS1/CYH1TbvLPWMAJjgWguhUuZ7mZk5wtJLdQFWPAHAi4aws4NshU3VYJfbJ0KqDzCJBad04tFobvhaNk4zsmBxDneh2SU90yRovA//Epf6f7fGT57wFD4Iac6qidHO/4TWg0i1r+G6U53lVLRTdBVFx8suiZOpTnsuPpbEqo68h7XYnKfc4tDdRzdkatPiyS5rcYymHAD6dsaB26dFLLXDvKlwbwxcRr0Tab4lrszlU/LL5y49V4oWPaZ4OvVU4hvlnRNbgNtubzBM0LnPtl2654OoCfDm3O9KpRHDi7PsqrBwkGIOh3ThMFp+SuFN3Cw26FyA8pvVh1TQ18tuHYoTMdkL7jV+icRVIuYyddVyAu5VIZqTHVUxrDpnK8S2XMDmF2duimHBrTcyFSgOeWN1/RPIDpcNk0h7mZM+ye21uGmW7IvdBPDjYK4QbW+4VNtsnQ9Oia0FmCc6jqjiccXdcY213Q4TEHvcjMCAYlB20ZHVObdxGcawmsa+HDHZOeOi8B/8Sl7f2/EWxVaRui/j/qpZ5loHug2oyGN2VK4VD+bqEDm1zu8wqga6S4dgURaBbpGEaltdzXtj23VTDnvpDO5O6OQ0TaBq3VMc0zUtnY9k5vmkCeHoq9p+zwXDLRsmTxFzzjoE114bbj/AFBRFRmbSBkJt7r9Wxp3T7roAEaZTgCTxcvpCaGufdbpomtqtabuOTp0TTENc2AcBWPwNCE0Esd5hJD/AN0yndTpycNyg2+o6BYBjG6cIeHOfAA5UxtVxa+RpouDibjhUONSM2D6pwtbDiO8qmLWbKicdeiaZuJBb07oi135jsi0Nf1DkyHGTt9ELtGyVZdiInBKZEOzr1TSC/N3ZVAOZpt6lPp3SZI7Si8Eg3aYwqcEhpxHVAz7noq7ZbDp7xqrhwlpxqe6w3TO5TACW4KoNtosHb+3xrL6PtlOF4IaYJ3CcwXNedVLxUsiW9JQFryby4P9KbTeXXy3y4TmN8q5jZuzHROcceWAfyKrTHoOupdrCt4W9RnKY69xLCMcwTHQ8io68T+ia1rGCEGtJtGHamFY12dhsEMjLu6q2uNx5gJCaLtSZRva8U28TRmXIEmoRpk56qhvbcYEQU9+CIyNEazCGg8XUQnue5wFM5OyIupNiWTrjCbUmkHOwd1BL76ZuHRFrrtLp3KItcWOdDTum88XDCMirj5hSBJeQG/uixopi4cxnVEHDmutYBlNxbb75UT/AKk99QOZTiZ1Ki1r7cpjKnmTPsCmiJZkhwKc4BnA4QOEppDRxZp+kptSXAMbAOQoubE8WsBUS2X2DbMp7+QuMBcDXAN5o9KpAlk8oOxTgLiG3f7JzmlxaBC8K01K7B3/ALvivD2P8xgxuuYmW4TaQBNWSHAxKkxcWW9EKtnBmNFTJL6jmTG09VUfYyXiX7KPN8OccysbABMnYKsMMZw2E5Gkqn6pY3B0VOIt5iPonFnl2QVS4apbHBbquGy7LcZKgtpy2oLDmU18wD+q9Rf+idJaHtOmsIVC4GoJbxZTyLnNjCYHW21NshXG02EXfm2V8jhqCSqj3luN08va4WS0kQIVzi/FSHbNTjIDnx3b0UDzDaBKEVJtHuN1a0BrYLhsSntbBZJL1cIDGDh/Mnhoa0zgaJlThIEHMJ1gNziSdihMwMTonExtpqrxeA0XR9FfwOm1/FagwATj2Q6dcpgDhnDk5kgmTnEq1oBJiNCqdrQRT03wpGmkadk4QCS4l26cBnXK+GeFNP7WoOM/3vEeDByz9F5Tmuh86RCY+cWdlXph7adptATHh7nMY7XJcEw510wnB3DENAOe6ZwGIl2yIPnU3O3xGsJwj1b6IiAbRaep3XhnOLeIEFvM7qpvdOrR6lZbU9Ud09rWNc7lXAbCKmCDnqvO4h/p5kwlo6/090BD5qc2h6KcAsNsdVLL4yXbL1uML7KqZE9JVLzL3aO6QqphsuvJbnhTqbXu+8dcROdkKUH7XInBT2hrrp4W7LFV7jlsanqh6W+j8SDuCcapzRTZLSTdoFGQSEIJ0V1MGxz+NcvC6XYRgRknKcwfaWMtnXKHBEGex2UgOd+LX2XmEy1zTjQndAl02sLXNEx3Rv4XEwRqFVaLbPRv2U6GOAaKyo83CkTaMKn4PxNQZphs6yvCfD20Tc83P/kOaHagFP8ABNJ4CW7p3hajZthOoVbhwwBrjVeW+lL4MeoAKrTNW0Elg1I6q4M1d7qr6nUzGdlT45DwZ0lQ2BcXOA0lYII2K5HMbJAH6OTmG+dRun5bDxg6ojzOGwFmkJ1Lh8trm06W+6IbIc0AkYlOBDjceABBwu/+yUMOdOwUc20mS5Ma8NIcAH7LinUjbCz6XXHQA7KoA/WOh7KAG203y5uclUZyXEmdT/soOrDjumtAyXTCZt5eic28b+6Mjeeie6nBuJaoYSRAJajhpNImScpsBtzsX5KuJqOFha3WQn4F9NtzgmMqOAik7OoQ8JXOPLgBN+GeINUONQNb0TfhouLnPydYCb8PoRkFyp+Go0+Wm1QB/OhQOisb0Csb+EfovJp/gCPh6R/6bV/C0vwp3gqJYW5g90Ph9NvKXBfwGfvCv/Tzs8Jvw+o0k8JJX8HW/A0exVbwVSo0tcw+6r0PEiy0PEdBqi14keXrrKq077TUuxu1U7m0xOp6oCwcOf6JgAbjACcA7snixuG+yZpc03dFB6d/ZBpsEsJym03WcpTPD+JMNqMc72X8JXAIZSMDTK/gKxM47Sv/AE1xm54Hsv8A0thi95MJnw+i0aEpvhKLf+mEGNHpH+SwOitb+EKxv4QrG/hCsb+EforG/hH6Kxv4QrW9Ao/w3//EACoQAQACAgICAQQBBAMBAAAAAAEAESExQVFhcYGRobHwwTDR4fEQIEBQ/9oACAEBAAE/If8Ay3Nf/mGzOSoCO0NxAWqhW08jU1sn/wA0jaoIdGz0xMh4UcGfCi3SzHIBKoG3zA3FO2pcYXI2RkWo8WU35dtkmMF9v/lrdHUu1otHUsLijs7nKcvGzxlchTdbueAGURGYfGLFUtsdpoL5XKXzDtcG4xQmGhweIzZyYN9R3BhwnD/8daIlB8d9070MHfxLL1WrdLxAEtbrf+EoFMFZeIagUwDbBhXekdg28XqMoSJpzbcPxLXgOQ48Mo+EEADLZopjmYSUFMF14uBYcRczCj/d/wD42Ez8Etaaxoililaxr4jk+XVc57jGQ/CIFqqPzEaglruUtYnMfRnWAnqU4l5SYrWZ0NfdgX0v1LVHzpzV15ufISz+I7Nt6QxcHQTzwsefcYszUsgDw/8Aw+VDAmjiAIqO7lK1z8mIm7iMQGqL0LnK3nBhQHKMhy6b8EWoootzfbEC0sxF0qtwKAjWl64Ax6iQoU4bgoF/QRxX1+D+8Bwpb9AS33yIy/AXgxLrLvUfcqgLozPF5k3f/vW/BBh64aRGYF6LmBheOUqUzMrQs0zLBSZNpg1N8sVMknTrwRTtkhCbAF6b9TAGcvBW/iVdXKKh4dBycszaoZOYWzoYF9TKBdQtlUBnTUyRie5AlwjZb7EoqwyWdkDLr23CgRp0IAb7aVF8ejBExr/2a2UwUAzGoOsc1zNB6ZWVe7nIE5LHedSmFH0uNIHlfLOFwpYrM1PueV9w9g1+EEzRWQz8wiyfURL1nmqu4UE/vmYgAeanmTA7YCPql5NfzSQYvooOvU6O0mUMGvJ5jC19I8EqYOzX7ECxv8yG4WXu8ToA65laqmAQG5P/AFuFDFs2WMbIRnHnl/SUqwPCUalPhFzc24cseOUkFvCGP1c5e2/mZLRpfxMUB4y9o+tN7EbZ8Z3LJXsrbFm3gtfeDxTfF3/qKCPk7iaA30VyoFdnIhS8RPSDh1aL+7KI0Lt5ZTQJxJr3QsHyRt0+gREZQ28cRIi77EvBjKMa6+SN/YZ/9NE1UoOVjIU5cSoQ2NxoavhZfzNEscOWEgBnz9iDd3035TkJAMwa2Og3+ZYLN2UjGlwOWTpljLcP3TZoooNsvMaliYAoird74lKhyAwVxM8D9MQmEOk1IuFMlYXnBUDIcAMLMLIPFHxDP6Zw+phhi9YaslbBoMV1MNbXT7zMj2QW5BkY2XmlGyZQhpOGYLw+SGf/ADcEXoxW2C3MqgX7PMsUI58S2xNoC3gHq2boDnhMTj2mNPg9fMWWul+dceJdopv/ACjNHrilf2lgWT7pnq0VQzD8qYPP+EDaNRX+JzhwXC5xVJm/VAqV0E4zBzIlxKHyB5Jhq6TTHtENAU7lnbR8Zjh4tDT3LCMF5hALMGjLq1p1BtyxcRTl6/F3Hi54phNUF24Y0QmDlCpZ/wCUX+ILMa07LhEbOWcy1zW+DEyricxiXXLR/MQTTg18xTlpUPzKZWn4jYmHE7dsfuYGNzORIa72sLh7UJ8Gcy0VY0vB9S1zAcl9QTftizETVCj+U5QWr+E5SleiWrvUt98G0zhjN+Jhychz5jGqt/4Sn57FTO2OTULlJ5RZ+ZnXRooptlOJgA1HPKINiY00Qy7BM3lC4pg2+KvI7/8AJ8YUG4DpVuN4jhCFFRJaragUyFKE/TUyJWztwWwVGRqMYOgz9YLBdL3OQVVMosott/HiV0gGx5lY5fN7rqMqHGKUnR4BxLiFWiOpftQuoX4fE0FMGF/CB6FvAMoBK7wDzKZ2FBYlYO4YMsWCqDMoQcGuZc2w2Y+kAUBuDfhhJQ/RIzReB67m4XwfSVZLdmNx871LJXv6gam4acxoPZ1/41AHt7itheQU37YFLxHObeIJGPeR1O9Y34QS1mUBOGrSfeGys3H7+oUbAuLX+UDlZR+RH6xawy+vEuGo/wBxHJcrD9A6l1JaNu2K8Pc8RxQK2CpS1U70hWG7jA6cw8G8PxBFK02sTDfm/wAdzNJwDcXY3q4Pj3LbkqXbfwmaYtmLr2yiwsjCYcRgMA8HbxNMabafcQxCkWps5zU4/XMBdROEoYK/hH1yzK2lh/4VRXRAMUuzKmAtdGY/Nl34j1FMAZY0ZqIy+UxVP9Mma48MsDkU+jEv3J98IwtCP6wZzgOIYtWg2uIVbDq5MtoW8iBaigKUURBgn6VtkrgttNihgrlz1Ln4Zogt7JedxYZlVTx5ub+KpWbirBew/vM4INDYfMWo/AQkbXTmXvatTMUzI39xDwlE45hUHMeM8h9pnlX9BFQwCEUpp+kYusbP/Ds9HjqI1LBp4hDhKB0lDWzFot1mbqNFg2gz8y4sOByiKDsqXbv1D6JZ/QCUxCyfupVbsO7cstUiYagLLq9OahYCXjIfrUvNYdPP74m6loQIOdIfn56g2tgVQd9RAg3Ov7QvBf8AWJntGjU3/B49y7VxAP11FBA6uO1+JauMsYpMxGaBRVZm8eSXO7UYvxSwjjtmaAZB2zAgttLqu1Exm4I4RTD2raRiGPLiBNpp/lKVks0rEIBkS/66qXs8K6ItaY3omtp01Eyl27JYWX6xiKGMFvmAaF6o29kLoj7bOxnNwnDBHnV8sEdFoYFropA0ftTT+3cpD4MdgUttl15XuIl1cbG4AAoM2mw/pzFEAH3hu04of1UM35mF4t06/bhnzYalVn1GYZwDkXiZWmqX3lpWRXl7jYs7Zg83LMXXBlqMMhXhIN8BdZMS2UtgSZky91xOFHRILvQeJVyWhpl9QsKxyJfH9dMQYiEcQYonMNVr/CZkzYNnxCk1DhZSpztPzAokcAahW18rs8kTauyRmNRb9n8Q9PlBHXTwpxAV4wOYlupFr3BssgwkuXDDo5mJbcDZKdKKp8xBnd5hHgbwfuo2FGIU7VTBMjbZ1KJC4umtMuD8Qs1nZ+8ycbgmvmMlzxGXpapRBfahUbExrbCXt8JSxX0McKmvSKBIWCDPo4MV9gmgbkr31qWKUGD8PU/r1BYPmZtKmjKrD3S1A2YPXid1SzUxab7KUQ87kuVNOXgvHARMkwYQYroSxanRKZwcWZK23VD8wXstVkiC2g0xRef1BlkVi+QqBYsdnU2VY4P5+ZRQrxf9iVsZaD8S8hXQ2E4SGeY0bC+OSLCgNS4ZQUTgSqhBcV3L5fTBuJSy9XUxvl0IlsHzUjbNmU2+JWQCQhHKoaHXlC2jYYp/EWkDmYoemmeSFK1R6hlMH0g2y+M+If1SX+Ii7tOYi3g6WrmmPm2ZvYlr3AeWre9fm56wd8lxja/7D4mUhjs2Ziu1XY/j9YSxa3x7jSQ6CJpt4NfMGtiOOI6C4oviWJleUaO7nmMCGjiDYzdwJYW7LEcyRaNywi5gfzBpbwcNByjYVgsxTQJ6Eaos6ARarEpVD0zd4zLnyCcvm5V7zqkWp3T+IIkVybXq5exR/J1NGBzzAUqMTiiLLLGxDmBFLs3maF2U4IiaHW3U5VEaQyii2f1WLsEKU29OJcdDgeIsOZlpArmjg4YjPxEY4xevUq5ViNj1Bdinmu445TW8kFXQSH7J057ySzi/Jmc+Tobh7GuI1EpFLoHMwlhe22UCsN5pshRfApduyGgye5kVVPH3MGS6Q4jKoeGPKOhy9wFXJ9X7qOWSFMXAd6Zgup4lcfs7jOn2Gpkjd2RtWw5ndxQtUuXJC/mSixWtWPtBFl5Pyl5g4BBDruoWdAaO5fmlB8tXp1EWtoXz/UVCupYQrhH4pZnmDDUaW0XoJMVlPEwIabcuZfPWKD7JZ4fqHMpjGiyWYS6tGZaN5gihK8eYPE6TSFAoLnWYa+iq6/FyvwDt+ZkN6mUqF3IK2y4vqVv5w/iaaspleZQwU7cxHYoq6S4DvSn7wuB/eJlt9iXWjWBYKHk1Bh2otbW4oah5Vz2xp2DvudtANi4ichDaMERgsqLrWt2wxDDyPvAUyP0JWluhi7nVU13xDNsdiZGPCytPzLXhLK2qF5kz/U7CYJQGT14HmBLPb6ih2YB1LU72nXDcYbkqqeJnMzuzBYOJ+sr0Ug4Y01y1KJseTmUCxzMfWUUqObNzdqbGuYxyPm4ReW8tfWOUbRgKWyi589EqOzbBG1Al8/Ewsq0LjqM/VClu2ufioWUU7RubHfU9yFpeIsRTw5josoNrx5jQ6ExbxEBnle4uXyCg6RO9cIspumrEMWoMlcFfuq0QKGqydeojUl5qlZ6HoSXqJXUPnLLxGsKw0zZ9OL1T+oXIDdBqLFUjZbLg+iYkBHfEEiil1qNsWnqEvN6xZfEHI38yxwBlDDt2bPDLhyOQ1HAYw27s6jyRPoObqBW8VcXmoPCVWDH+00Rd3SGz+WDTq17jXZdp+JZWW9qwEfBdoFWbyZrEwGJdeohiuyrh5WymoeAdN1LF2pDESnax7aV4CIykVy6mXQXtBTjRvJqJb8aPzCtZ5WSWb2GTnshpnOcoCEsbwAzDnJMZz4OI+5jluBZfRbyRxTQK+v8ATWjMYWTAvbCv2nSdCaLP3I2C6MSnXuGsFNxKptpNhjFA4IF5czd0W3ZRyY4CUL4PjmWHgTpzXv7Qq3Oa0yNGtCviKu28aNfrMNw3h59wEp3Wq17ijjOtouw/xX7cKjC3whVm/pxG3KOVR2kaIhULPsxTHad+Y41H7UYTJKtUuzY0/wCpzVyfMOMDg1OTY7ZgEsbLds1m6Z5haOm8+IxVhTdZ9xCrPcw5kMjtngLf7RHyeUDO7VCHKUmSu2LOzVt58QAU1UMqrk/pA81ZCb2LeoQXgrd470+fj1M5RvEx01vjU3NvzslObTxm4RneIuhE35xE0JTCc/6nKnkSgDcSkfBQvc3RooWtwXU1MW/mIqsY25jUYu1yfUa+W/RP3/MwFNOCKB2a2gbLy0M2Ntk/CVXLh2ivrng68QRWxaeZi2DraWBui8dJW14jHoWtNwjQFVjib+jw/dxyXBL1C/r8yuVQ5hBqVMF9eZQHmtO4WRbASo1BoZuYBVXU6uKupRYrTlMEcq9mGEeQf4mLraO7an9IqLnUq3ALb9VShWlY/umKHEIlppNwubhK2dwCRZNflOIinIlGwXycTB1cA46h6AZv4JlxnZZ1A0pRVVJl5QVWFfMQxCsZh16liqlPAQWXCYXhgWWXZ95slJaFLNud1MQls/TxFVV86SxzadfibzOiQ2CfOVpBwOJlmDbLM58IB2YcV+Jiadh9o4ZnwigFFypL6A6n2lb7HU2hQ4aYatil+XqPIUHDLAAZPP5lKWW4ISUe8IK0VUNqdjohqmEVzK1yf6Sk9Frj1DFU09piCGlfdnEXc0i94ByPfuFw68/5gRxLNovlhbpj5h0SuGGzd5EwV8ha3LbTey8QguajTFwGwWWspc2PLx1OZqtvwhLlNaeOoD2Hk1CMgOyPVQO/2pZQM6Y1te53HG2jluBS4Jfx95RdlcjamW2xeZ7XjwlUwMq8ZuGRTwI0GiBk8S7JToSg2YKu5QUIYfMy5lkk4Ga0K+ZYsNuqiXqa23PEXEAkSL+tGuQBw6lxog036lSijmm/UMwW4lsw4OulbjCLDddf0mr9mVO5WP5ly0Vkpp3H2Fqa0TgcMmV9yhqw55fMxZWi8qZplvhwkxZlbyoNnf4JS+3znMU5l8Wnf4qZFNtNpXINVBmUczbRtAd1xAe5wdmNC2t8e4v5tvCBQYdrmFclXO4s79F1McggE5Zcqh+1CmwwNHMpmwCs7J0Y1Jj6y5jHabZQDBqVW4zdxCiLcvl4g0PdnllJVbUiXODuHeY9G0M7lH+UQvFtcPE4l3tfcNIcTFwFlpUuv6AbuKwLdLvzDBBB0u/DL346f0VSZeCt8NQ2sKyrbNriC9xrTp2cDqajzbNMakrdOF4jkrvsdEZWkJdQandJqsPJGrA9GYuaE7MZ4Dthpmb0pCi1l0XxLFFuiVQKqwzF0OGB3U5WJb2gMy62EYu3C+43pUtZdxVThguJkyWNGI0bPp+JUoDUn4ROSQE0y6OJwV5ckY4jhn5l8V0Fw2BKu4s84cEwFYOMMq6kglqDNcVAaFG3mBlqeyXdxjhipV8Bu0VEVpwfSBFK1dsX5la13k1cv+FPh/o9RE9w0HbhB4ilFTjNxZfUHQtTYpuPBF6Xf9kwGLts6e4Vy+nUy7rcfui6TUaAL1XM8aeFDY4XL8IfrH/aWii2tflAKCb2zKFlyrshaKmELhi2rlELcwJzlmgKBvL99/EwZtOZ3MGbmgQtf/emzaxRNcFKyn8z2XAamS1WUaG34gsxe7pYwVlvM3SWX6iYvBuoEBVmKmDf725fYHwgWs2gG2PSZxKVFLBRRpT3MgICFZE4LPEorh2hArKyeYuXEy/iB4op/QvTZQhdgLwswgxk6goGWklTT4PEa00Ns9DCrLSUIPvqyXhh3XfDaArLnDxmpZoseRRg2fMoraFtu+4y1ZoydQ0jJ23+sWyNv6ZlAyyNIi92vhG+d4FQC5s7bfU0ZcUmYMppd0d/M3I3QaPUQw1wOmFDcnvXqGRqacPqFvTXLmPaXITEU5yU9ioJUdtv8Quuif6JXWlb6IUijy3ghdVAtV8yysVVDcSNWMepYV1h7lBhFTyo6JIOLZlYBm3mLX1qN4lqs6A3Fyo7uSw2AUL4ldYtlfEacINJlxHGs+Zoev8AvWbWsYmcTKej2y7G/wBvibC1ywuVgrDCdBqfi4rzDuz/ACe5y04OYX7QA33HVt9qfdl1YOMM1LFlAp1CuLpYWTYcDNMGKCps6l7bmytng+0NtfCiggN0jVcwaJeQfadq0ZH7zKObpauI3J0yibg77ngXywZdxlx6gK3R75ZpgowZSy66MUUbVpgU6GlPbHl9IyrMUTxAlweH5g1rw3UKqhUw+8FmMpkH5g/oVhx1OXYaI4ms7GfcwwDKlCYAqm3MRZZpR9oOXJYqKoWuRYWnovg+YRZFz/P/AHZjHN3ATPPsPPmGCaCsfUh2pTbWYcOTgzMpGIl+5diDzBs5FV4uFKy/I8mPx0gx4l6Utan6zJJWVLLNHoiUrvYwJRSrfp8amIFTmnMb0RN2RoKk+hfMoguHRjwhCFO7j5uaao5ZmTw4QaYMPLHLfeLbgw1whWwANmUxJ8xF4uIbmjl6JmC6jfNmvmFOALo5Jmy6HcLBFPbjzKKMV3+ZssNME7Le614/ENX2RO/4nPTs/SV7V8QjQrlupbwXgtwvXcdrK7qfmLMan5aiR458bI45e46BQBTA3SIJ8pl0V/3NsmbpnEvPLYOpSQasNozhND2RXzX8AJeghLrVeIZdd0W/KII2wVs9yrF7KdTp3QZ+swAALz8x3a95eJaHhYM+Tv8AsRrwG1t+UeQFWKnKnuWnJWLi4ltqtMeJaLJvnmZ13WQ+8syQMGeGIwChqXLXFQ29VpYXjvIfvUG7g1iCY0iQenYxZoro3CVUIsEfOblNqjr9e5gh4P395mUolmWXVq/NL7YzJijRBTAotUWlh2KliBe8qLWx+7lx6QJZTyuowNlfDDPIE1fUxIngEAN+RmSeH/b7SK2s1wcRoUAooIBs8Q/CVijcNPhinL1Y0wPC8viL+NgwfXqXAA09JQGQXNxBVacKfSXLAUzx5jGxzjfiUdVnpXhiLJRWKlEwyqcYl7xMy5jqOZyIN8ajJEVZx+I1+GFRRpXTdQGVa8W19Ia2sfMUbB5Di4N+O7zLCVR0cxw0VLu8xMAEFz7mQBq8CWvstC7Tm2ZKfmYEMN5l+jw0RDevMRoB5YdaP3Hgl3eW7w78RxwKFv4grq7gZ/1C3mx4dRdQnA/yeYFN8aoWuhvx5ic7eWHHR0cxSV16JfctyxKu4f8As696Uxh7JRdrLJjdLaBiKuT1i+5icQw7jOrRVd3KEyDGG4AQ6yHY8zqInJxLF4M2/M0SJ80M3aheT/CPaXWB+/ucaa9DMtlzrLzDOtKy1m/UyDfV6IUpvCs4lMZZcfiU9BG2AxVlz0RMXGgoPE2g0+GWsFzX4hmwF8Rb6scH4l8cLheI5a8LvnuNtBYFYJaCzRDirT0dxOAdBBjj6cvOlDb74HWT9xlkiig1BQFjOGoGqyk1xPncJdeIwl0zRzJFBc18wgrO1rzmJTFBBYBvQZYWEdTELV8ax1HRdix/7Vyd5cyrRYhj4ALUmNf7EntYVj4m8jn6fUEIAtmb7h4cgyOpS7TO2cdy8ohBuU142dS9WoNmpZ9BtGOUIAaZp6GjnPSCZwKQ4hyyv4iQ8+e5mHl9CoQBsxTcSo/RLgWsvlj0+8pTEN+Zg0x+/vMbtUqZpiKZA7FojV4INrwzJir0ji1ZFdSwlsukuYrg4fENHNUTWhDFu41uQdD7jwWXg8dviVsEXZpUXLHCo6AeT+P+BaAv5k9FeJULd+PcsJbd4jbYenUNog9IYoUhw3C+RYKFvynEtldjMzIU7vvOxVP+1OlbY+TNaRygXhH3I4lIcn7QIjfwX2MzgNJAWaX/ABnNV9JdRF5bBm0h8+0xIWRheyVlTfK8R4mHDa8zOiJvDUwRnAcxEYg+BPXmakH39RRb5r3CGDPPn6QUtDpFUi1Rbu/Vy1KnzIhhk+E/czOYDyy7FUTOO5Ztpjblgdm13T6RHRWv2lnZeGXM2VHI1/Et9JvwJgOa0XPzABm3xx1KyPg8/eImCg5/qQoXwt/WcFIXKZJvmw/iUa5NncaZfc9IQrK3HVeJainIpoEurqrtAgbrii2JVo/cO2GutVukFiLPfEc/Jxk8THeYo/8AU+JIN2u07v8AtA0TUXH5whMrgyytDIO/cqflJ5h9+pd+0G0a8WVcc/TmkQUDnMMzWGQqu4ysr4DLCCLxBYzoIO5T5IxVUv1viFU3Fm6zK4JuhmEs8rDv3Lt6rKu/2o0U2gPvK2Ou8MFWA1IUwIZQda1Sqc/3h4Xg9E5Btw3fiC6BO83FXIFf2EKGCkBwWul36l1Cl6IJtxtZg92yPqdQEYm2GzTMaLNiS7OCSzdovh6p3C0dCOvKPqsOgiacHafZA3Eh9JY1DVvdTOgBlUPVZ2D8JQ5Sb7RNkwb9mO7GzWKjWHb/ANawt4O/ErjDK8EzC4qG5wrbE1RGFLVYGE8wK2mpp8pa3tPmjUl05M/M+swhuP3eIUYqhW0LlrVL8ymvJVfGuI1Airq3ULGq1yRtasdcfEoEK2HExM42wBAJB7FfM63TUi5R28YS2hC8DJFWqMQNTLBo3+EHFw5Jdbjvyywp3ENVt6SNGLtuWVlE0fzMttl931nbRcofyiH6yhChlpgCSSFTSaA5ldSugMSjRFhpMGUNF9xwhG0NLiiim/nBguqazjyto5xv1KbxAgKvpxKYpafHmWeXsR2QGpU2cJnOE5MQh7pPrD/laLi5vavggoqh52xvRyceItIExx3JtumM8alctU24GJgEKWDNOIAVTC76jvRxFimmUEuh9yI1dfF1DkZe2viAmgNnE6TYtl5QVTqD6oK1MtH5h0lr9wiLkUWiNvwQuL4Dw/M3Friok1ZGLxLSox5ILblMAUSzR8AmNFuuWZZN6YP4TDPzh9QWu2cdRVCsIMCaTNdHmERwMmEDY0qvtjOJnK5JpEG8YhsKjkHHuNiFtm3URbuVmDAlgMkTah1MBKzqjY/W5cOM3SW/EKgJY8ERropG4yXDJUrHTOqLYWb/ALQvMOnMqotkEVv4f85spYSl0RS5ftFNiPYEs5GeH7orrhQ7fHxOH5xvCeJsNa9SDSx6xPKDPKYWA6/zD6UwJHA11XxKPk5a9y3ozJA3BYOmC3EGk2L30Sp1ybwNsdCsfMoidAd+kFYeJBVCly2FCkPZ8wTc7UJZd9dKAb5zFgHiw2zcwGGzPz1LBUuogqDCmCLTV2bYUrR6JQQO3HuA9i+TMLIBZPEK4KdIV6GcJUXWAOSU2S4LzM5UWX4z1AC4uA1HacqKa9zICzqYg3ghmm/cAY9tVyvXmXCN+johrXVoyXK0tj8HiGDQdAzUoUYcJBXof8obsFnzXxohbbgXZNVGTkJ3iyos7/E7AebEsQd0RdwVeRw/Eu6MpvhKEFrJ1BVkPg+kC8NqhX1xqF3+hKSmDJdxJlbK/iDKKuIVaATtKgba6lwLjvX9iNbn/J2GG1i5W+YY1f16X5AUUWwtBBuQNG3MQA4MbIAyh85tj81f7pu/JwTkLbIx95RtZgC59y6pHc1KeAeYjErlojYFNeQ8yoJmaHELloHkw6ovRBXJwbKR3KTkWXVdygFHg4hGNCafxMaw+TiXhQ3tn6EYNhbtJZk57s5U0TPlj7SUGSmhHa1emadkpnuO2NV/zoNgGoAF1yrUDUVoQixzHKZuoCGnqZWgOHHmoKVHy0HMpLHMexDgI54AnvID+YCj0o9PMoo6jiVrQsU77lBU6ZYs5C5RX22JcMtTLEbm4DDEmRTtnqYaLc1hequjPylUxGRrfHmLRHbT7I3BZF68zJhcjj4lbAwyfZEwOBE14IP93HuYKCKGdS7olWZnbFfz5g2oHKN2nRBA0niVEYmA5OmXk1eZxHG0ETZmzDAoGd7wSAK7v7EbAV5JuCtSlk47jtoNM05gaj52IjA0PpBXLaMH4RurvEkreg7wZ+sqBzk3Ut1AzRAulNd6IlfHII/IH/m1b1cwqq62hdVpe3dSg0/hyZTGXjJ7lDYm2oqIuHIoqA7g1ceyG4tlGjDwfD4nBQv9+WJBdy/MbficmJglS2gHE7wajoef98hYVVgxjsgwoXZv3K6Hd5epWb4cVQLsBI0uPSC8Wr8lN1KlsWqLqQrsZ9JpZli9VuFaUObeY2bHV9yMbD0mObHJ5gHW3SmYNy6UOoguq/JXUXlSEYXFxATSZtogmNFq/KB2BYLxMTgyyM1CQkJxGYRdo3K0WatOZYwhMNn+0aLHSzGbRvZONStc6mBxx/gZVO6OvEBLZ8zLqybmWPmExpLHRMi3TiO35p/zmU+ZsydIt19qXuK3exV7i2Hkw49ypC9DTXTNvwMj8xi5uu6qHPD6tU9y1RCK8vcV/wBrMZYpG9W76jqWwI+qWFMjLB7LhtezbmWTyYfZU20aZJlmRqx8wbY+ghqYOKMwUVrLDSe5mJpTKLHIz7qUb7G5cylEWczfF3avrAkBvAzeONh7lpLrg6ZU54CGhKSlSqqOvLAB105ddS0ab5NMdcxRs9y2ITXt58zMka089QgUo1dM9TuQ1TfuAFSgi89QNbXm0zJizKNeRLcDMCKsgXnDEx0tNA5jvBl4QsLrCtjFOK23aIaKehCbhCqMItVDaQ1/zeLG8yQQ9pkWPXUZ+aepb7UHVU0VdUGEpauqjl8sMrHg6uPcIDyixIM/giFUqMhgx8rKC/gSoK8BpmscvuXmXgt9Z9TnjHaZIBima4PU4pCFTthzKXsM4fiX5Q3D95YO1WhSCc1Lm8R+zVwkC3jn7IR7r6JOiD8I1Qjc+8QlHByR2fg6lcvbfumdI6M+4PXB1KllG11DOR8EinrPa5n32DUzll1FSqnXHv1AAVq/gQjcTwrXPqbBiV1TxHVYbDNSq3bGxCMsqA35JqAOe72yq2/VytGaZKKYOczIrZqhEMNuWd0h/wCRXFuL/hYwhKsN4bjdknxRzuQpSlSxZm5sGeb4MeUSqy+8r6wUz6E52OY3EIVshi5XV0N/4RIuYxnUfAex/WIRZgXHBnT8QFC9YxEKAplrvMo21uh</t>
+  </si>
+  <si>
+    <t>Hikvision PTZ 4 MP</t>
+  </si>
+  <si>
+    <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAYEBQYFBAYGBQYHBwYIChAKCgkJChQODwwQFxQYGBcUFhYaHSUfGhsjHBYWICwgIyYnKSopGR8tMC0oMCUoKSj/2wBDAQcHBwoIChMKChMoGhYaKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCj/wgARCAQ4BDgDASIAAhEBAxEB/8QAGwABAQEBAQEBAQAAAAAAAAAAAAECAwQFBgf/xAAXAQEBAQEAAAAAAAAAAAAAAAAAAQID/9oADAMBAAIQAxAAAAL9UAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAgrI0goAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJz3iMc9chiwi0y0MtQu+dO2+Oz1Xj2oAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAADn5+nGOXL1cTz59EOGfTzOKeg5PTDhveidIPV6vJ6wKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAct845cO3I556Qxz708e/SMTpDGrS9uez2Xl1AoAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAcy8s84ct5Oc3ky1CSiUGpo1146PR6fD6DuloAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAcBy52NYQZuSSwksAALZTVyN6507+z5foPYKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAR4zfC2IuRLkZ1kSwiwAlBZRZRZS42Onu+Xs+kzqgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAGZ4I6b8fpCwmbCSwksEuSxCkKCgoLZRZRrIe75ez6rl1oAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABh82Hn1xOn0PnfRJLCZoksJLDMCY6ZNc+uAobxo0C3NLZRQ8Wd+M+l9H5o+w49qAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZvCPLj35PHPVklzk3nMNMDUyNSCoAEBYFgqC3I3edOl5015+9OfP1U8/0vPk9zOqAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAHIhYxNQzjeTM1CSwgEsEsAJLkENWCgFIoWUWUVRVJpS+ny6PSKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAzybiS5EQmNZIQSwgAIoyomdwytICgAAWUoKlNXNNAstO3TyesCgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAHPpwjSwkuSRkSwgJLBLAAACKMqIsAAAFlFlFlNJS2UtlHTnD1paAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAxmahnWSS5JnWSSwgICAAAAlACAiwKIBZRZRZS2DVlLZSg138vpKKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZ1yhbCS5GdZMywhBLBLCKIAAAABKIsEoigBZRZSgtlLrOi2UnTEPSKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAnPSLnWTMsJnWTMsEsEsIACAFIolCUEsAAIohSUALZS2UtlLZS51TtePagAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAOW8biZ1kksJjUMgzLCywgAJQAAAShKIsAAEoAAtlFlNA1ZS2Uno83oKKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZ1gmpYkuSSwzLkksICAgAAAKCKJZSKIQWUgAAALZS2UoNXNLZR0xTsKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAc+nONAmbCZsJlBmwAksAAAAALKJQSwLACAAAAtlFlLZS2UtlKQ9CUCgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJjUiywkuSZ1kmdZEsJLACAAAsAsKABKEsAIAAAC2UoFlNXOi2Uso6659AKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAwmoSwmdYGbCZsJLBLABAAAAoAABCywAgAAALZQC6zoWU1ZSgvbh3AoAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAADnrOoSwzLDOdZJLBLkSwSwAAAWCoKABKAIsEsCwAAtlFlGs6FlLZS2Ud+HcCgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAOW8bhLkkuSZ1kksGbBLCAAY38w4ejyeM+lOHQ4e75P1h0vyj3+P2Dz+7nxMdvBo9ePd8sv2Pk8j7HrzogAKCgtlLZS2UtlJ6PP3KKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAEOe86iSwmdZJnWSSwksICAAfH+wOPzvrw+R1+lTj4Pqjjw9w+d29VPmvo0+fj6cPmdfcMfO+oAIACgoLZS2UtlLZSduXQ2KAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAS5M6zqJLDMsMywksJLCAgAAAAAKAAQssBSAAgBQBZS2UtlLZS2Ubxs6CgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAEoy1I+BfNg92fHk9ePHzPdPnYPpT5WD68+Pk+0+HD7t+DT7t+DT7t+Fo+5fh0+4+KPtvij6+/z3c+0+MPsz48Psz48PsT40PtT4sPtT4sPtPiD7d+JT7V+Po+xr5Wz6evm6Pozw0933vyv64WgKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/PcfX4zkmjnz6cznz6YOeN4MZ3gzLAC2UtmDq4ZO+eI6znDpeVOt4j068lPZfJs7zFEsJLCFFmjesdDe87Nbzou+fU6/qvzn6MAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA+P8/6vyjlQxy68znz6YOfPpzM8+nMksFQucZNSAgqBZQAgqCgvTlT0Xz9SywJS6zo3vGzpvGze86HXl1Pofe+P9gAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA8PxP0H54xqU543g5Y3g546czGN4MnMuAgJWSsQ2wNMjTI1cDowOjno0lLc06b46NrC6zo30xs6bxs3rOh159D7X1PnfRAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAOX5j9V+TNazkc/N6Tnz68jHPrzOfO8yZsJLkucwoJVI1TDro4O8OLrgyok1BZDq56N3NN9OWjepo3vn0Om8bN68vc6bxo/R+3y+oAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAfkf135E3w74Pme/w+4xz6czHn7eUmbCZvIklC0jv2PN366OW+vIayKgsU559eT5/P6HM8c7cjKw105U7XOjXXj0OvTl1N7x0PL6fL7TdlP1Po4dwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAB+S/W/kjedZJz6cznz6cDzctQkvIxiiadjPo10MddIcZCzmNMK6OY6XkO2vP1PTnh6I48vXzPn4+h5a4g114bOu807dvN6DrvGzes6FlP1fbj2AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH5L9b+TNZ1knPpzMeH2/MEox5evIV1L6Z2hoHHWCYhAUKAAsU1vls9Tj2jHH0ZPDw93nrio7b4dzXXj0PXvn0N6zooP1nXl1AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH5L9b+SN51kzjeDy+L08CZ6cDzxTXqx6C7lipkznpTljqrPt93Nj5WPR5bnLOJ06xoxJlfXJ3MdudNkjPHvg8GPX5anp83Y7azT09/N6Tes6KlP1nXl1AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJ+T/WfkzebDOOnM+dmbM+b1+I5dceovfGxZYS5JpmuXq8XsPsfP14tcJjpma4493KdPJ1503x9njXXt8HuFZjrLCA4+f2cK8fXGz0qN+vxe03rOyWU/WdeXUAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAfkv1v5I1LCcuvE+Z25dzPz/oeA31z0N2WLZRneC51mvL6vL2PZ4vR47nt08249jz85eKdK9vzvf4Fnu8ftEuTrLIksHHrzOHn9vjr31TPs8nqOus6FlP1nXl1AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH5L9b+SNSwnHtxPnduXUng9/gO3Xl2Fli3NKZFlryXpwPTxaTjemCGzn65yWc51NejOollN51kSwko4ef08a9Wpoz6fL6jrrGjSU/WdeXUAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAfk/1n5QSwzy7cT5/bh3M+D3+A69/P3LYi2UoMW8q35qM3UGsjcyM56QnbmPS83Q6dcbiEJLBA4Y1ivXrOjPp8vqOus6KlP1nXn0AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH5f9R+bOGbCcuvI+d24dC+L2eM134dy2WKlLZS5tPNj0865AAAAHQnadS5siSwhAg4Y3mvTrFHq8nrOm86J05ek/VUAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAHwPv/ACD5edcy8uvE+b05bLx6cydcYPQ47Ol56jVlKC50OWPRk8r1Zrzu9PP07U5ddoRBLBGSyYNznkorpc0ezxe06axofQ8H1z7gAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAHl9UPyWenA68d4Pl7xovPeS8u/EoKC6wOmuNO14I9F81PTfKPU8o9Tyj054DtnkrpnIQIoko1NZNAe3xe06XA6fo/zv7A2AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAD4Px/1X5c8vp8fpPn1C51Dpz65ORQCgWUigIAoCiSqgEqIKiiXPQmdZKC+zxesm/N7D6f6T530gAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAB+V/VfNPgcenM8E3gA6lPO68hZQCgFiWWggCioIAgIKELqiY6cygvr8nqOvo4foD6upQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABKPynj/VflDyc+3EZ1zPWoxz6w4XWCgoFlAgCgCoogICAm1FUef0+U6KL6vN6T1/rvD9AoAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH579Dk/A8fqfNMcvTs0sMzUM8+sOF1kqUWWAAAKKSyAISmgpomlHk9nQ8zUL9z537M6UAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAOHyvuD5f0N0/MfH/AH35w+LAkozjpDlOkM2Q0zSiKlCCzNBampRVFlKfXOf6q7Pm+T7g83qlAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAEo+X+b/AHHnPw76HzySwk1DM1DW8bMztk5XoMa3iM87KKhVpVJ29H6g8X2FAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJ876Q/I/M/f/LPyc+x4DzTUJYO2caOvLNOnKQLTN11OGvqfWPi/d+nozoAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAEo+V839OPyXm/bQ/n793g/Dv3/E/Den9j1PynT9SPjfX0AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAP/9k=</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +419,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -450,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -458,6 +471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -760,13 +774,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" customWidth="1"/>
+    <col min="1" max="1" width="38.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,7 +800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -803,7 +817,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -823,7 +837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -843,7 +857,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -863,7 +877,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -883,7 +897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -903,7 +917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -923,7 +937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -943,7 +957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -960,7 +974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -980,7 +994,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1000,7 +1014,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1020,7 +1034,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1040,7 +1054,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1060,7 +1074,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1080,7 +1094,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1100,7 +1114,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1120,7 +1134,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1140,7 +1154,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -1160,7 +1174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -1180,7 +1194,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1214,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -1220,7 +1234,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -1237,7 +1251,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>73</v>
       </c>
@@ -1254,7 +1268,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -1271,7 +1285,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -1291,7 +1305,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -1311,7 +1325,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -1331,7 +1345,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -1351,7 +1365,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1371,7 +1385,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -1391,7 +1405,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -1411,7 +1425,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -1431,7 +1445,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>98</v>
       </c>
@@ -1451,7 +1465,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>100</v>
       </c>
@@ -1471,7 +1485,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>103</v>
       </c>
@@ -1491,7 +1505,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>107</v>
       </c>
@@ -1508,7 +1522,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -1525,7 +1539,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -1542,7 +1556,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>114</v>
       </c>
@@ -1559,7 +1573,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>116</v>
       </c>
@@ -1576,7 +1590,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -1593,7 +1607,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>120</v>
       </c>
@@ -1610,7 +1624,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="2" t="s">
         <v>121</v>
       </c>
@@ -1625,6 +1639,23 @@
       </c>
       <c r="E45" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1235</v>
+      </c>
+      <c r="D46" s="3">
+        <v>5</v>
+      </c>
+      <c r="E46" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
